--- a/www/download/COUNTRY.MLT.WIOD13.xlsx
+++ b/www/download/COUNTRY.MLT.WIOD13.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.821684755536959</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.839100636076563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898078280441284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.904384898541739</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.929851826238597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01871863654664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04756224641374</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00792264839678</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.877192137997102</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.802021683764487</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.804162377075274</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.793408381912368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.724495030641948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.679660773115357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.716576242819136</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.295623166253744</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.17596069392481</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.422439075330671</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.311889000055085</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.133889411471156</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.0852247913352564</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>-0.188576719776036</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>-0.105057260178602</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.00199895381962811</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.0827262498746555</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0370051749651952</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>0.0822072309582282</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>0.014940201059255</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>0.00096366991322383</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>0.110390569763568</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>1.22007812922352</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1.08323291572656</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1.52485371780442</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>1.32413348515073</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1.01495468403701</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.934892346590012</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.462168693208995</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.629352583073705</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.918455416493603</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.896277009039295</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.905519303717878</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1.00453538622117</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.93189794982559</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.853080566854119</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1.11051921296029</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>1.86954464021598</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>1.72797995272948</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>2.33267377613644</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>2.04663789535924</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>1.7025904262969</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>1.62492941685665</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>1.00589335056468</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>1.22626204246157</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>0.671574911142481</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>1.61195972188083</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>1.65426951847101</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>1.73795293359323</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>1.62980634052659</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>1.31864023256208</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>1.69168046385998</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>307833478.704107</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>306266660.535439</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>265418982.77816</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>284600281.319239</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>325779350.720895</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>359788159.17823</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>297849433.284441</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>311444320.844682</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>314647147.587674</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>298486778.618352</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>279948558.489809</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>310424668.548809</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>311515722.487444</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>317282207.623997</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>276673060.347074</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>99089723.0459217</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>106134848.895005</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>86570462.2458659</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>94677772.0587103</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>109637939.817902</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>115046272.944031</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>131160623.634574</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>140055541.082736</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>154697343.947979</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>121113851.622106</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>122482498.226379</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>119828933.713333</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>130880074.544293</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>146003708.150769</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>126666757.708984</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>1806604.02077174</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>1787356.96514213</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>1641877.02789732</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>1635404.13646905</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>1808675.93603383</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>1877753.84941141</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>1712356.18089929</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>1666960.2045624</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>1418764.38664817</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>1272774.0608792</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>1092940.89734785</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>1218997.90306884</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>1003674.31489507</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>898559.841125864</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>934937.96051092</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>1023.9796317015</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>1036.15226171218</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>1033.6015456093</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>1042.19639611116</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>1079.23020027375</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>1135.57966917236</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>953.385379299043</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>1150.37051621626</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>1146.19427549197</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>1267.71302832736</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>1328.96596846584</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>1405.02712773466</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>1586.82081268657</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>1672.36250814249</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>1533.26365293706</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>2396.56768897382</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>2402.0968434955</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>2068.35333822455</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>2205.66307257811</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>2579.62665579798</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>2964.21129143372</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>2389.61038449804</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>2554.42747198595</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>2779.81171056157</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>2906.15389302161</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>2919.17215530772</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>3392.53602197156</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>3851.46308656329</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>4342.9334709808</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>3532.53390638339</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>1.4218411677151</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>1.27107557932874</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>1.79542256084558</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1.59151957512734</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>1.26817586258693</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>1.18594669489125</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>0.654156597127359</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>0.83141165583137</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>0.585589219975193</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>1.06893987378227</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>1.05989509655453</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>1.11883614359153</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>1.02139041377676</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>0.859109517351654</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>1.08933061662603</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>932.89922609</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>960.840655929839</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>875.659035093602</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>989.085623425908</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>1044.17556978661</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>1078.08081156199</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>862.207646516561</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>856.263656253718</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>1091.10530276278</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>1192.32536178964</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>1235.63480864315</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>1427.83139407664</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>1647.62884320037</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>1868.02223162769</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>1817.70585291811</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.821684755536959</t>
+          <t>809.135223506135</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.839100636076563</t>
+          <t>862.849749419046</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.898078280441284</t>
+          <t>701.002067445134</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.904384898541739</t>
+          <t>756.157512118822</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.929851826238597</t>
+          <t>863.952847245511</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01871863654664</t>
+          <t>896.452323890273</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04756224641374</t>
+          <t>995.353040647428</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00792264839678</t>
+          <t>1042.43384854996</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.877192137997102</t>
+          <t>1160.83537921562</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021683764487</t>
+          <t>922.387540539497</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.804162377075274</t>
+          <t>920.105642315296</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.793408381912368</t>
+          <t>881.485414614039</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.724495030641948</t>
+          <t>933.13900751605</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679660773115357</t>
+          <t>1017.42077190265</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716576242819136</t>
+          <t>876.631862853392</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1149539.50861004</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>14497519.9444561</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2207546.51110763</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>20120507.2010442</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>45784755.8826167</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>61881741.839875</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>82812159.1143556</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>99547470.4528552</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>104423192.805247</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>40938245.8455117</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>56193849.9458278</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>75514519.1939575</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>91907252.3511967</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>117085676.087988</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>96800734.5384127</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-36704390.2322299</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-26767605.8013263</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-39466907.4558665</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-27191900.018185</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-9996859.91370851</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1945534.73920816</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>39767359.1543619</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>41074642.2305404</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>49600964.4898047</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-19574169.3564781</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-3947343.31800094</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>11740529.505399</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>12147339.5008703</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>22339774.7456447</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>-2991203.63446486</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>37853929.74084</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>41265125.7457824</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>41674453.9669741</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>47312407.2192292</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>55781615.7963252</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>59936207.1006668</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>43044799.9599937</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>58472828.2223147</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>54822228.3154422</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>60512415.2019897</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>60141193.2638287</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>63773989.6885586</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>79759912.8503264</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>94745901.3423429</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>99791938.1728776</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1646.46979865772</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1909.12550066756</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1840.6080634501</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1908.36436170213</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>1895.32110091743</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1867.72315653299</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>1886.23824451411</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>1891.49664019548</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>1831.5737905695</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1959.59699453552</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1646.46979865772</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1909.12550066756</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1840.6080634501</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1908.36436170213</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1895.32110091743</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1867.72315653299</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1886.23824451411</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1873.06478468084</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1894.42083037815</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>2183.75432366237</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>2112.65111979316</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>42.23</t>
+          <t>2044.26726001742</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>31.19</t>
+          <t>2297.17374123947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>15.47</t>
+          <t>2486.67624060495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>8.51</t>
+          <t>2847.25664877912</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>2432.65066122194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>2722.81729745513</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>3059.03083731146</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>3345.33148452363</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3577.48983631473</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>4339.13982305009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>5320.73796135974</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>5961.29617365826</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>4978.86495064032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>121.98</t>
+          <t>95185966.0459553</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>108.3</t>
+          <t>96143845.5682564</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>152.46</t>
+          <t>86830805.0226806</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>132.42</t>
+          <t>96589296.3758287</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>105.19</t>
+          <t>116249909.841644</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>93.47</t>
+          <t>137270806.385901</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>112653155.920866</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>62.91</t>
+          <t>119864821.788595</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>117962160.357384</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>89.63</t>
+          <t>111101978.243895</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>106287800.69609</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>100.44</t>
+          <t>129029565.022465</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>93.16</t>
+          <t>136033176.397246</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>133907472.419554</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>111.05</t>
+          <t>100597515.525997</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>186.91</t>
+          <t>3077.55815565765</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>172.76</t>
+          <t>2989.78848671855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>233.24</t>
+          <t>2760.72266341456</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>204.68</t>
+          <t>2924.43956971278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>175.21</t>
+          <t>3136.08578646415</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>162.46</t>
+          <t>3538.13613509204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100.57</t>
+          <t>2954.38987457375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>122.59</t>
+          <t>3079.71544903443</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>67.14</t>
+          <t>3638.92937598667</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>161.2</t>
+          <t>4078.39464551972</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>165.42</t>
+          <t>4367.58618560208</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>173.78</t>
+          <t>5158.88821386639</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>162.94</t>
+          <t>6223.19467713802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>131.86</t>
+          <t>6853.35799509956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>169.16</t>
+          <t>5595.79028406079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>234337293.716977</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>240646734.020936</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>187079361.122612</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>207072130.177054</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>259699771.595503</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>301712244.365545</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>276897154.251209</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>274490946.071707</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>306828216.757887</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>249933748.275555</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>260277035.935389</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>297097526.248786</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>317765317.641326</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>329586166.866828</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>257166174.394972</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>-893.803831995282</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>-877.137366925392</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>-716.455403397146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>-627.265828473319</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>-649.409545859193</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>-690.879486312916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>-521.739213351805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>-356.898151579299</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>-579.898538675215</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>-733.063160996098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>-790.096349287349</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>-819.748390816298</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>-902.456715778277</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>-892.061821441303</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>-616.925333420476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>307.918</t>
+          <t>-139151327.671022</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>306.323</t>
+          <t>-144502888.452679</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>265.454</t>
+          <t>-100248556.099932</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>284.588</t>
+          <t>-110482833.801226</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>320.289</t>
+          <t>-143449861.753859</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>359.857</t>
+          <t>-164441437.979644</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>297.932</t>
+          <t>-164243998.330343</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>311.548</t>
+          <t>-154626124.283112</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>314.687</t>
+          <t>-188866056.400504</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>298.522</t>
+          <t>-138831770.031659</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>279.973</t>
+          <t>-153989235.239299</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>310.421</t>
+          <t>-168067961.226322</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>311.623</t>
+          <t>-181732141.24408</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>317.332</t>
+          <t>-195678694.447274</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>276.685</t>
+          <t>-156568658.868975</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1385.82335</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1423.35312</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1377.26698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1476.38768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1473.61581</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1515.93832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1418.21509</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1626.93416</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1868.283</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1984.44397</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2041.98878</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2193.14696</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2538.99753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2825.1127</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2576.19549</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>131.528</t>
+          <t>0.0410136913964132</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>132.109</t>
+          <t>0.0378419888838688</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>132.636</t>
+          <t>0.049854921270469</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>134.476</t>
+          <t>0.0446816578637466</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>136.295</t>
+          <t>0.0389820431414413</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>137.834</t>
+          <t>0.0422392543053772</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>118.833</t>
+          <t>0.0469750470274093</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>140.257</t>
+          <t>0.0581789451500173</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>129.738</t>
+          <t>0.0485873751351189</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>130.205</t>
+          <t>0.0430144139298502</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>127.448</t>
+          <t>0.0519026318067934</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>128.563</t>
+          <t>0.0427509708895946</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>128.346</t>
+          <t>0.0516064997395292</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>122.178</t>
+          <t>0.0377693618234957</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>120.087</t>
+          <t>0.0303318712434236</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>99.104</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>106.148</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>86.578</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>94.674</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>107.666</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>115.059</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>131.174</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>140.079</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>154.711</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>121.111</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>122.485</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>119.834</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>130.898</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>146.007</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>126.67</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>142.15</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>127.08</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>179.52</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>159.16</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>130.97</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>118.57</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>83.11</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>58.54</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>106.9</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>105.99</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>111.87</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>102.11</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>85.91</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>108.93</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1.807</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1971.81963499446</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.642</t>
+          <t>2014.16080919266</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.635</t>
+          <t>2105.0491934226</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>2187.32487864978</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1.878</t>
+          <t>2220.06132249716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.713</t>
+          <t>2341.96233993632</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.667</t>
+          <t>2416.85037926708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>2406.06824787509</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.273</t>
+          <t>2461.64909418327</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.093</t>
+          <t>2512.31847011829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.219</t>
+          <t>2574.27894368699</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.004</t>
+          <t>2626.41985086363</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>3048.45170473549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>2961.89450481308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1616.02247943738</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1733.12184215755</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1770.48890676647</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1850.65172602171</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1922.98613329567</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1951.74472640863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2073.73783740309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2140.18170002683</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2124.94077630928</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2160.56270123431</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2203.17336956751</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2255.01404420631</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2299.23424464493</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2670.20692419726</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2593.97155767355</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1358.93245775653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1357.14530249966</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1348.45227957022</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1444.88629912096</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1442.58140055067</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1511.2096245237</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1361.36418745232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1530.27083571207</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1758.04608065702</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1859.37692854773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2062.21746388007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2187.51092659218</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2732.02415924076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2811.66718714088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2575.92271309126</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>131527773.490009</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>132109117.02421</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>132635689.349404</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>134476290.241573</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>136295270.91966</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>137833669.263885</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>118833303.022133</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>140257011.824327</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>129737837.27676</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>130204934.758125</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>127447813.064936</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>128563139.080731</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>128345935.249053</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>122177986.855328</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>120087381.584778</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>138874.446687167</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>139488.262001645</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140044.246782362</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141987.657087953</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>143908.239551269</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>145532.567350409</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>148518.699858705</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>151325.446256559</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150581.137128626</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>148818.629624851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>150919.65916683</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154191.416391832</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>159111.861238722</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>163839.80861896</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>162466.36194054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>122463.736798588</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>123005.017926314</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>123495.302319692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125209.060997641</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>126902.689385716</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>128335.071345203</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>131772.967257186</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134354.368171712</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>133263.808734455</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>131304.73504799</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>133117.864507571</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135939.780428245</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>140257.853856829</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>143503.761848436</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>144492.532243455</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6810.28788</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6759.79225</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6504.52899</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7022.21424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7201.39947</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7612.00423</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7085.95531</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7660.96435</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9137.04683</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10679.72391</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>11410.39724</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12906.4076</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>15298.69514</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17266.45712</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16001.56341</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3197.71274</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3308.85405</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3245.0926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3439.99494</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3473.64834</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3454.01761</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3389.1217</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3747.28687</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4407.92382</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4884.07563</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5167.44378</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5505.79668</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6530.86134</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7612.71384</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7102.18183</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8540.10449177539</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8906.54079634492</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9298.47153182451</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9715.44255502075</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10129.7218552802</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10575.0429322389</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10878.9484176219</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11000.1283463253</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11266.8232314971</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11529.1787391199</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11932.1325426299</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12320.7451710381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12719.6954845692</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>12822.9626287163</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12793.4869850017</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD13</t>
